--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/DELAWARE_2021.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/DELAWARE_2021.xlsx
@@ -1273,7 +1273,7 @@
         <v>14</v>
       </c>
       <c r="D51">
-        <v>0.009402283411685695</v>
+        <v>0.009402283411685697</v>
       </c>
     </row>
     <row r="52">
@@ -1975,7 +1975,7 @@
         <v>14</v>
       </c>
       <c r="D90">
-        <v>0.009402283411685695</v>
+        <v>0.009402283411685697</v>
       </c>
     </row>
     <row r="91">
@@ -4189,7 +4189,7 @@
         <v>14</v>
       </c>
       <c r="D213">
-        <v>0.009402283411685695</v>
+        <v>0.009402283411685697</v>
       </c>
     </row>
     <row r="214">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C241">
@@ -5629,7 +5629,7 @@
         <v>14</v>
       </c>
       <c r="D293">
-        <v>0.009402283411685695</v>
+        <v>0.009402283411685697</v>
       </c>
     </row>
     <row r="294">
